--- a/The FullMoon Festival Linup.xlsx
+++ b/The FullMoon Festival Linup.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="237">
   <si>
     <t>THE FULLMOON FESTIVAL</t>
   </si>
@@ -35,6 +35,12 @@
     <t>Name on Poster</t>
   </si>
   <si>
+    <t>Where abouts on Poster</t>
+  </si>
+  <si>
+    <t>Checled Name on Poster</t>
+  </si>
+  <si>
     <t>Size</t>
   </si>
   <si>
@@ -47,6 +53,9 @@
     <t>Yes</t>
   </si>
   <si>
+    <t>Middle</t>
+  </si>
+  <si>
     <t>Hendo</t>
   </si>
   <si>
@@ -68,12 +77,18 @@
     <t>Rachel Pardoe</t>
   </si>
   <si>
+    <t>Bottom</t>
+  </si>
+  <si>
     <t>Scott Hoy</t>
   </si>
   <si>
     <t>Tap Man</t>
   </si>
   <si>
+    <t>Top</t>
+  </si>
+  <si>
     <t>Roy Duggan</t>
   </si>
   <si>
@@ -98,523 +113,624 @@
     <t>Small</t>
   </si>
   <si>
-    <t>14:00 - 15:00</t>
+    <t>14:00 - 16:00</t>
+  </si>
+  <si>
+    <t>Callum Dunn</t>
+  </si>
+  <si>
+    <t>Is this peter dunn?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bottom </t>
+  </si>
+  <si>
+    <t>*Missing an Hour*</t>
+  </si>
+  <si>
+    <t>Callum Dunne or Peter Dunn</t>
+  </si>
+  <si>
+    <t>16:00 - 18:00</t>
+  </si>
+  <si>
+    <t>Ben Maskell</t>
+  </si>
+  <si>
+    <t>18:00 - 19:30</t>
+  </si>
+  <si>
+    <t>Blair House Project</t>
+  </si>
+  <si>
+    <t>19:30 - 22:30</t>
+  </si>
+  <si>
+    <t>Barry Fearon</t>
+  </si>
+  <si>
+    <t>*Barry Fearon? Who's etc</t>
+  </si>
+  <si>
+    <t>22:30 - 23:45</t>
+  </si>
+  <si>
+    <t>Matty B</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Adam 'Sol' Cairney</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>16:00 - 17:30</t>
+  </si>
+  <si>
+    <t>Anima</t>
+  </si>
+  <si>
+    <t>Yeardos</t>
+  </si>
+  <si>
+    <t>17:30 - 19:00</t>
+  </si>
+  <si>
+    <t>Infrared</t>
+  </si>
+  <si>
+    <t>19:00 - 20:30</t>
+  </si>
+  <si>
+    <t>Alan Stacey / Stevie Butt</t>
+  </si>
+  <si>
+    <t>Yes Stevie or Ste?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Middle </t>
+  </si>
+  <si>
+    <t>20:30 - 23:45</t>
+  </si>
+  <si>
+    <t>Groove to funk Djs (Nijafingers/Audiowok/Mo Beats)</t>
+  </si>
+  <si>
+    <t>Bottom and Middle</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>13:00 - 13:30</t>
+  </si>
+  <si>
+    <t>Seb (Live)</t>
+  </si>
+  <si>
+    <t>13:30 - 14:15</t>
+  </si>
+  <si>
+    <t>Paddy</t>
+  </si>
+  <si>
+    <t>14:15 - 18:00</t>
+  </si>
+  <si>
+    <t>Otty / Masked Collective</t>
+  </si>
+  <si>
+    <t>18:00 - 19:00</t>
+  </si>
+  <si>
+    <t>BACK2BACK2BACK</t>
+  </si>
+  <si>
+    <t>ReVival</t>
+  </si>
+  <si>
+    <t>Neil Cowie</t>
+  </si>
+  <si>
+    <t>Yes?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top </t>
+  </si>
+  <si>
+    <t>Colin Cowie</t>
+  </si>
+  <si>
+    <t>Ricky Rooney</t>
+  </si>
+  <si>
+    <t>Roy Campbell</t>
+  </si>
+  <si>
+    <t>Travis Bradshaw</t>
+  </si>
+  <si>
+    <t>Travis</t>
+  </si>
+  <si>
+    <t>Kim Bezance</t>
+  </si>
+  <si>
+    <t>Robyn Freestone</t>
+  </si>
+  <si>
+    <t>Paul Moran (TBC)</t>
+  </si>
+  <si>
+    <t>HOTWAX / VOLUME</t>
+  </si>
+  <si>
+    <t>15:00 - 16:30</t>
+  </si>
+  <si>
+    <t>JK &amp; Mikey J</t>
+  </si>
+  <si>
+    <t>16:30 - 17:45</t>
+  </si>
+  <si>
+    <t>GOMH</t>
+  </si>
+  <si>
+    <t>Yes but its G*O*M*H</t>
+  </si>
+  <si>
+    <t>17:45 - 19:00</t>
+  </si>
+  <si>
+    <t>Chris Walker</t>
+  </si>
+  <si>
+    <t>Chris Walker?</t>
+  </si>
+  <si>
+    <t>PK &amp; Tom Doyle</t>
+  </si>
+  <si>
+    <t>Middle and top</t>
+  </si>
+  <si>
+    <t>20:30 - 22:00</t>
+  </si>
+  <si>
+    <t>Pq &amp; Yeardos</t>
+  </si>
+  <si>
+    <t>22:00 - 23:30</t>
+  </si>
+  <si>
+    <t>Cal Davies &amp; Fionn Mcard-Rooney</t>
+  </si>
+  <si>
+    <t>12:00 - 13:15</t>
+  </si>
+  <si>
+    <t>John Bolton</t>
+  </si>
+  <si>
+    <t>13:15 - 14:30</t>
+  </si>
+  <si>
+    <t>Joe Matthews</t>
+  </si>
+  <si>
+    <t>14:30 - 15:45</t>
+  </si>
+  <si>
+    <t>Lewis Parry</t>
+  </si>
+  <si>
+    <t>15:45 - 17:00</t>
+  </si>
+  <si>
+    <t>Dylan Fearon</t>
+  </si>
+  <si>
+    <t>17:00 - 18:15</t>
+  </si>
+  <si>
+    <t>Jaime Craig</t>
+  </si>
+  <si>
+    <t>18:15 - 19:30</t>
+  </si>
+  <si>
+    <t>Lucy Todd</t>
+  </si>
+  <si>
+    <t>19:30 - 20:15</t>
+  </si>
+  <si>
+    <t>Cal Davies</t>
+  </si>
+  <si>
+    <t>20:15 - 21:30</t>
+  </si>
+  <si>
+    <t>Jacob Kneale</t>
+  </si>
+  <si>
+    <t>21:30 - 22:45</t>
+  </si>
+  <si>
+    <t>Fionn Mcard-Rooney</t>
+  </si>
+  <si>
+    <t>22:45 - 00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle McKee </t>
+  </si>
+  <si>
+    <t>12:00 - 14:00</t>
+  </si>
+  <si>
+    <t>The 3 Stools</t>
+  </si>
+  <si>
+    <t>14:00 - 15:15</t>
+  </si>
+  <si>
+    <t>Roy Campbell (Progressive House)</t>
+  </si>
+  <si>
+    <t>15:15 - 17:00</t>
+  </si>
+  <si>
+    <t>Pippy &amp; Hoff (Progressive &amp; Trance)</t>
+  </si>
+  <si>
+    <t>17:00 - 19:00</t>
+  </si>
+  <si>
+    <t>Cal Davies &amp; Pq (B2B Trance Classics)</t>
+  </si>
+  <si>
+    <t>ROOMTOUR</t>
+  </si>
+  <si>
+    <t>PK - 2 sets</t>
+  </si>
+  <si>
+    <t>PMIX</t>
+  </si>
+  <si>
+    <t>Will Mosley - 2 sets</t>
+  </si>
+  <si>
+    <t>Harry Pack</t>
+  </si>
+  <si>
+    <t>Burg - 2 sets</t>
+  </si>
+  <si>
+    <t>Tom Caine</t>
+  </si>
+  <si>
+    <t>Tom Meakin</t>
+  </si>
+  <si>
+    <t>Finlay Mackie</t>
+  </si>
+  <si>
+    <t>Trav B? Yes</t>
+  </si>
+  <si>
+    <t>Uk dj (Scott providing)</t>
+  </si>
+  <si>
+    <t>??</t>
+  </si>
+  <si>
+    <t>Petz</t>
+  </si>
+  <si>
+    <t>OUTDOOR STAGE</t>
+  </si>
+  <si>
+    <t>15:30 - 16:45</t>
+  </si>
+  <si>
+    <t>Eclipse</t>
+  </si>
+  <si>
+    <t>*Needs Checking Can't find"</t>
+  </si>
+  <si>
+    <t>17:15 - 18:30</t>
+  </si>
+  <si>
+    <t>Dusty Plankton</t>
+  </si>
+  <si>
+    <t>The Dub Lhunes - The Dubbons</t>
+  </si>
+  <si>
+    <t>19:00 - 20:15</t>
+  </si>
+  <si>
+    <t>Ideal Forgery</t>
+  </si>
+  <si>
+    <t>Lady’s Darts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:45 - 22:00 </t>
+  </si>
+  <si>
+    <t>Balla Sabbath</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>The Uninvited</t>
+  </si>
+  <si>
+    <t>22:15 - 23:45</t>
+  </si>
+  <si>
+    <t>Infared</t>
+  </si>
+  <si>
+    <t>13:30 - 14:45</t>
+  </si>
+  <si>
+    <t>Spotty Dog</t>
+  </si>
+  <si>
+    <t>15:15 - 16:30</t>
+  </si>
+  <si>
+    <t>The Settle</t>
+  </si>
+  <si>
+    <t>Mother Funkers</t>
+  </si>
+  <si>
+    <t>18:45 - 19:45</t>
+  </si>
+  <si>
+    <t>Sammy J - Sax</t>
+  </si>
+  <si>
+    <t>Local DJ’s (TBA)</t>
+  </si>
+  <si>
+    <t>21:30 - 23:30</t>
+  </si>
+  <si>
+    <t>Fish56Octagon</t>
+  </si>
+  <si>
+    <t>Headliner</t>
+  </si>
+  <si>
+    <t>23:30 - 00:30</t>
+  </si>
+  <si>
+    <t>THE PUB</t>
+  </si>
+  <si>
+    <t>Reservoir Rodeo</t>
+  </si>
+  <si>
+    <t>1.5 hour sets?</t>
+  </si>
+  <si>
+    <t>The Dub Lhunes</t>
+  </si>
+  <si>
+    <t>Maybe another act</t>
+  </si>
+  <si>
+    <t>18:45 - 20:00</t>
+  </si>
+  <si>
+    <t>CUNF</t>
+  </si>
+  <si>
+    <t>20:30 - 21:45</t>
+  </si>
+  <si>
+    <t>Clash Vooar</t>
+  </si>
+  <si>
+    <t>A Stones Throw</t>
+  </si>
+  <si>
+    <t>13:15 - 14:15</t>
+  </si>
+  <si>
+    <t>14:45 - 16:15</t>
+  </si>
+  <si>
+    <t>Ladies Darts</t>
+  </si>
+  <si>
+    <t>16:45 - 18:15</t>
+  </si>
+  <si>
+    <t>Red Hot Chilli Yessirs</t>
+  </si>
+  <si>
+    <t>18:45 - 20:15</t>
+  </si>
+  <si>
+    <t>Index of Alice</t>
+  </si>
+  <si>
+    <t>20:45 - 22:15</t>
+  </si>
+  <si>
+    <t>Shark</t>
+  </si>
+  <si>
+    <t>Lizzy and the Bifters</t>
+  </si>
+  <si>
+    <t>Alice Dudley</t>
+  </si>
+  <si>
+    <t>18:45 - 20:-00</t>
+  </si>
+  <si>
+    <t>Name of Act</t>
+  </si>
+  <si>
+    <t>Stage Name</t>
+  </si>
+  <si>
+    <t>Day Act is On</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time Start </t>
+  </si>
+  <si>
+    <t>Time Stop</t>
+  </si>
+  <si>
+    <t>Description - Band or DJ</t>
+  </si>
+  <si>
+    <t>Bunka B2B2B</t>
+  </si>
+  <si>
+    <t>Bunka</t>
+  </si>
+  <si>
+    <t>DJ</t>
+  </si>
+  <si>
+    <t>Dan &amp; Parker</t>
+  </si>
+  <si>
+    <t>Tapman B2B Travis</t>
+  </si>
+  <si>
+    <t>Cameron</t>
+  </si>
+  <si>
+    <t>Dan &amp; Hendo</t>
+  </si>
+  <si>
+    <t>Nathan &amp; Cal</t>
   </si>
   <si>
     <t>Dunn</t>
   </si>
   <si>
-    <t>Is this peter dunn?</t>
-  </si>
-  <si>
-    <t>*Missing an Hour*</t>
-  </si>
-  <si>
-    <t>Callum Dunne or Peter Dunn</t>
-  </si>
-  <si>
-    <t>16:00 - 18:00</t>
-  </si>
-  <si>
-    <t>Ben Maskell</t>
-  </si>
-  <si>
-    <t>18:00 - 19:30</t>
-  </si>
-  <si>
-    <t>Blair House Project</t>
-  </si>
-  <si>
-    <t>19:30 - 23:45</t>
-  </si>
-  <si>
-    <t>Barry/ Matty Brand etc / DnB</t>
-  </si>
-  <si>
-    <t>*Barry Fearon? Who's etc</t>
-  </si>
-  <si>
-    <t>Saturday</t>
-  </si>
-  <si>
-    <t>Adam 'Sol' Cairney</t>
-  </si>
-  <si>
     <t>T4</t>
   </si>
   <si>
-    <t>15:00 - 16:00</t>
-  </si>
-  <si>
-    <t>16:00 - 17:30</t>
-  </si>
-  <si>
-    <t>Anima</t>
-  </si>
-  <si>
-    <t>Yeardos</t>
-  </si>
-  <si>
-    <t>17:30 - 19:00</t>
-  </si>
-  <si>
-    <t>Infrared</t>
-  </si>
-  <si>
-    <t>19:00 - 20:30</t>
-  </si>
-  <si>
     <t>Alan Stacey / Ste Butt</t>
   </si>
   <si>
-    <t>Yes Stevie or Ste?</t>
-  </si>
-  <si>
-    <t>20:30 - 23:45</t>
-  </si>
-  <si>
     <t>Groove to funk Djs (Nijafingers/Audiowok/ Morris)</t>
   </si>
   <si>
-    <t>Sunday</t>
-  </si>
-  <si>
-    <t>13:00 - 13:30</t>
-  </si>
-  <si>
-    <t>Seb</t>
-  </si>
-  <si>
-    <t>13:30 - 14:15</t>
-  </si>
-  <si>
-    <t>Paddy</t>
-  </si>
-  <si>
-    <t>14:15 - 18:00</t>
-  </si>
-  <si>
-    <t>Otty / Masked Collective</t>
-  </si>
-  <si>
-    <t>18:00 - 19:00</t>
+    <t>Seb (Electronic Acoustic)</t>
   </si>
   <si>
     <t>B2B2B2B2B</t>
   </si>
   <si>
-    <t>ReVival</t>
+    <t>Hot Wax</t>
+  </si>
+  <si>
+    <t>Vinyl</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>TBA</t>
+  </si>
+  <si>
+    <t>RoomTour</t>
+  </si>
+  <si>
+    <t>Will Mosley</t>
+  </si>
+  <si>
+    <t>Freesoul</t>
+  </si>
+  <si>
+    <t>Otty</t>
+  </si>
+  <si>
+    <t>Burg</t>
+  </si>
+  <si>
+    <t>PK B2B Roomtour</t>
+  </si>
+  <si>
+    <t>RoomTour + Friends</t>
+  </si>
+  <si>
+    <t>Room Tour</t>
+  </si>
+  <si>
+    <t>Outdoor Main Stage</t>
+  </si>
+  <si>
+    <t>Band</t>
+  </si>
+  <si>
+    <t>The Pub</t>
+  </si>
+  <si>
+    <t>Silent Disco</t>
+  </si>
+  <si>
+    <t>Mix Tape</t>
+  </si>
+  <si>
+    <t>Revival</t>
   </si>
   <si>
     <t>Niel Cowie</t>
   </si>
   <si>
-    <t>Yes?</t>
-  </si>
-  <si>
-    <t>Colin Cowie</t>
-  </si>
-  <si>
-    <t>Ricky Rooney</t>
-  </si>
-  <si>
-    <t>Roy Campbell</t>
-  </si>
-  <si>
-    <t>Travis Bradshaw</t>
-  </si>
-  <si>
-    <t>YE BUT TRAV B?</t>
-  </si>
-  <si>
-    <t>Kim Bezance</t>
-  </si>
-  <si>
-    <t>Robyn Freestone</t>
-  </si>
-  <si>
-    <t>Paul Moran (TBC)</t>
-  </si>
-  <si>
-    <t>HOTWAX / VOLUME</t>
-  </si>
-  <si>
-    <t>15:00 - 16:30</t>
-  </si>
-  <si>
-    <t>JK &amp; Mikey J</t>
-  </si>
-  <si>
-    <t>16:30 - 17:45</t>
-  </si>
-  <si>
-    <t>GOMH</t>
-  </si>
-  <si>
-    <t>Yes but its G*O*M*H</t>
-  </si>
-  <si>
-    <t>17:45 - 19:00</t>
-  </si>
-  <si>
-    <t>Chris Walker</t>
-  </si>
-  <si>
-    <t>Chris Walker?</t>
-  </si>
-  <si>
-    <t>PK &amp; Tom Doyle</t>
-  </si>
-  <si>
-    <t>20:30 - 22:00</t>
-  </si>
-  <si>
-    <t>Pq &amp; Yeardos</t>
-  </si>
-  <si>
-    <t>22:00 - 23:30</t>
-  </si>
-  <si>
-    <t>Cal Davies &amp; Fionn Mcard-Rooney</t>
-  </si>
-  <si>
-    <t>12:00 - 13:15</t>
-  </si>
-  <si>
-    <t>John Bolton</t>
-  </si>
-  <si>
-    <t>13:15 - 14:30</t>
-  </si>
-  <si>
-    <t>Joe Matthews</t>
-  </si>
-  <si>
-    <t>14:30 - 15:45</t>
-  </si>
-  <si>
-    <t>Lewis Parry</t>
-  </si>
-  <si>
-    <t>15:45 - 17:00</t>
-  </si>
-  <si>
-    <t>Dylan Fearon</t>
-  </si>
-  <si>
-    <t>17:00 - 18:15</t>
-  </si>
-  <si>
-    <t>Jaime Craig</t>
-  </si>
-  <si>
-    <t>18:15 - 19:30</t>
-  </si>
-  <si>
-    <t>Lucy Todd</t>
-  </si>
-  <si>
-    <t>19:30 - 20:15</t>
-  </si>
-  <si>
-    <t>Cal Davies</t>
-  </si>
-  <si>
-    <t>20:15 - 21:30</t>
-  </si>
-  <si>
-    <t>Jacob Kneale</t>
-  </si>
-  <si>
-    <t>21:30 - 22:45</t>
-  </si>
-  <si>
-    <t>Fionn Mcard-Rooney</t>
-  </si>
-  <si>
-    <t>22:45 - 00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle McKee </t>
-  </si>
-  <si>
-    <t>12:00 - 14:00</t>
-  </si>
-  <si>
-    <t>The 3 Stools</t>
-  </si>
-  <si>
-    <t>14:00 - 15:15</t>
-  </si>
-  <si>
-    <t>Roy Campbell (Progressive House)</t>
-  </si>
-  <si>
-    <t>15:15 - 17:00</t>
-  </si>
-  <si>
-    <t>Pippy &amp; Hoff (Progressive &amp; Trance)</t>
-  </si>
-  <si>
-    <t>17:00 - 19:00</t>
-  </si>
-  <si>
-    <t>Cal Davies &amp; Pq (B2B Trance Classics)</t>
-  </si>
-  <si>
-    <t>ROOMTOUR</t>
-  </si>
-  <si>
-    <t>PK - 2 sets</t>
-  </si>
-  <si>
-    <t>PMIX</t>
-  </si>
-  <si>
-    <t>Will Mosley - 2 sets</t>
-  </si>
-  <si>
-    <t>Harry Pack</t>
-  </si>
-  <si>
-    <t>Burg - 2 sets</t>
-  </si>
-  <si>
-    <t>Tom Caine</t>
-  </si>
-  <si>
-    <t>Tom Meakin</t>
-  </si>
-  <si>
-    <t>Finlay Mackie</t>
-  </si>
-  <si>
-    <t>Trav B? Yes</t>
-  </si>
-  <si>
-    <t>Uk dj (Scott providing)</t>
-  </si>
-  <si>
-    <t>??</t>
-  </si>
-  <si>
-    <t>Petz</t>
-  </si>
-  <si>
-    <t>OUTDOOR STAGE</t>
-  </si>
-  <si>
-    <t>15:30 - 16:45</t>
-  </si>
-  <si>
-    <t>Eclipse</t>
-  </si>
-  <si>
-    <t>*Needs Checking Can't find"</t>
-  </si>
-  <si>
-    <t>17:15 - 18:30</t>
-  </si>
-  <si>
-    <t>Dusty Plankton</t>
-  </si>
-  <si>
-    <t>The Dub Lhunes - The Dubbons</t>
-  </si>
-  <si>
-    <t>19:00 - 20:15</t>
-  </si>
-  <si>
-    <t>Ideal Forgery</t>
-  </si>
-  <si>
-    <t>Lady’s Darts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:45 - 22:00 </t>
-  </si>
-  <si>
-    <t>Balla Sabbath</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>The Uninvited</t>
-  </si>
-  <si>
-    <t>22:15 - 23:45</t>
-  </si>
-  <si>
-    <t>Infared</t>
-  </si>
-  <si>
-    <t>13:30 - 14:45</t>
-  </si>
-  <si>
-    <t>Spotty Dog</t>
-  </si>
-  <si>
-    <t>15:15 - 16:30</t>
-  </si>
-  <si>
-    <t>The Settle</t>
-  </si>
-  <si>
-    <t>Mother Funkers</t>
-  </si>
-  <si>
-    <t>18:45 - 19:45</t>
-  </si>
-  <si>
-    <t>Sammy J - Sax</t>
-  </si>
-  <si>
-    <t>Local DJ’s (TBA)</t>
-  </si>
-  <si>
-    <t>21:30 - 23:30</t>
-  </si>
-  <si>
-    <t>Fish56Octagon</t>
-  </si>
-  <si>
-    <t>Headliner</t>
-  </si>
-  <si>
-    <t>23:30 - 00:30</t>
-  </si>
-  <si>
-    <t>THE PUB</t>
-  </si>
-  <si>
-    <t>14:15 - 15:45</t>
-  </si>
-  <si>
-    <t>TBA</t>
-  </si>
-  <si>
-    <t>1.5 hour sets?</t>
-  </si>
-  <si>
-    <t>16:15 - 17:45</t>
-  </si>
-  <si>
-    <t>*Can't find them*</t>
-  </si>
-  <si>
-    <t>Maybe another act</t>
-  </si>
-  <si>
-    <t>18:15 - 19:45</t>
-  </si>
-  <si>
-    <t>CUNF</t>
-  </si>
-  <si>
-    <t>20:15 - 21:45</t>
-  </si>
-  <si>
-    <t>Clash Vooar</t>
-  </si>
-  <si>
-    <t>A Stones Throw</t>
-  </si>
-  <si>
-    <t>13:15 - 14:15</t>
-  </si>
-  <si>
-    <t>Reservoir Rodeo</t>
-  </si>
-  <si>
-    <t>14:45 - 16:15</t>
-  </si>
-  <si>
-    <t>16:45 - 18:15</t>
-  </si>
-  <si>
-    <t>Red Hot Chilli Yessirs</t>
-  </si>
-  <si>
-    <t>18:45 - 20:15</t>
-  </si>
-  <si>
-    <t>Index of Alice</t>
-  </si>
-  <si>
-    <t>20:45 - 22:15</t>
-  </si>
-  <si>
-    <t>Shark</t>
-  </si>
-  <si>
-    <t>Lizzy and the Bifters</t>
-  </si>
-  <si>
-    <t>Alice Dudley</t>
-  </si>
-  <si>
-    <t>18:45 - 20:-00</t>
-  </si>
-  <si>
-    <t>Name of Act</t>
-  </si>
-  <si>
-    <t>Stage Name</t>
-  </si>
-  <si>
-    <t>Day Act is On</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time Start </t>
-  </si>
-  <si>
-    <t>Time Stop</t>
-  </si>
-  <si>
-    <t>Description - Band or DJ</t>
-  </si>
-  <si>
-    <t>Bunka</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>DJ</t>
-  </si>
-  <si>
-    <t>Band</t>
-  </si>
-  <si>
-    <t>Seb (Electronic Acoustic)</t>
-  </si>
-  <si>
-    <t>Hot Wax</t>
-  </si>
-  <si>
-    <t>Vinyl</t>
-  </si>
-  <si>
-    <t>Volume</t>
-  </si>
-  <si>
-    <t>RoomTour</t>
-  </si>
-  <si>
-    <t>Outdoor Main Stage</t>
-  </si>
-  <si>
-    <t>The Pub</t>
+    <t>Colin Cowie B2B Neil Cowie</t>
+  </si>
+  <si>
+    <t>All Stars B2B2B2B</t>
+  </si>
+  <si>
+    <t>Ecstatic Dance With Rosemary</t>
+  </si>
+  <si>
+    <t>Wellness Village</t>
+  </si>
+  <si>
+    <t>Wellness</t>
+  </si>
+  <si>
+    <t>Slow Flow Yoga With Leanne</t>
+  </si>
+  <si>
+    <t>Live Guided Meditation</t>
+  </si>
+  <si>
+    <t>Open Chill Zone</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="hh:mm"/>
-    <numFmt numFmtId="165" formatCode="[hh]:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -662,10 +778,8 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -892,8 +1006,9 @@
     <col customWidth="1" min="3" max="3" width="48.88"/>
     <col customWidth="1" min="4" max="4" width="18.25"/>
     <col customWidth="1" min="5" max="5" width="15.63"/>
-    <col customWidth="1" min="6" max="6" width="8.13"/>
-    <col customWidth="1" min="7" max="7" width="14.75"/>
+    <col customWidth="1" min="6" max="7" width="20.0"/>
+    <col customWidth="1" min="8" max="8" width="8.13"/>
+    <col customWidth="1" min="9" max="9" width="14.75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -928,145 +1043,223 @@
       <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="H4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="5">
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="C6" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="C7" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>14</v>
+      <c r="G8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="C9" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="C10" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="C12" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="C13" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="C14" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="C15" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -1085,327 +1278,428 @@
       <c r="E19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>8</v>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>27</v>
+      <c r="G23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>10</v>
+        <v>50</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>27</v>
+        <v>50</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>27</v>
+        <v>59</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>27</v>
+        <v>62</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>62</v>
+        <v>71</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>27</v>
+        <v>50</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41">
@@ -1424,104 +1718,154 @@
       <c r="E41" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>8</v>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="42">
       <c r="C42" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="43">
       <c r="C43" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="44">
       <c r="C44" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="45">
       <c r="C45" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="46">
       <c r="C46" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="47">
       <c r="C47" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="48">
       <c r="C48" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="49">
       <c r="C49" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52">
@@ -1540,419 +1884,541 @@
       <c r="E52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>8</v>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>82</v>
+        <v>12</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>27</v>
+        <v>94</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>27</v>
+        <v>50</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>27</v>
+        <v>75</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>27</v>
+        <v>50</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>27</v>
+        <v>50</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="78">
@@ -1971,195 +2437,271 @@
       <c r="E78" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F78" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>8</v>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="79">
       <c r="C79" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>27</v>
+        <v>50</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="80">
       <c r="C80" s="1" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>27</v>
+        <v>50</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="81">
       <c r="C81" s="1" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="82">
       <c r="C82" s="1" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>27</v>
+        <v>50</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="83">
       <c r="C83" s="1" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="84">
       <c r="C84" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="85">
       <c r="C85" s="1" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="86">
       <c r="C86" s="1" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="87">
       <c r="C87" s="1" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="88">
       <c r="C88" s="1" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="89">
       <c r="C89" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>27</v>
+        <v>50</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="90">
       <c r="C90" s="1" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>27</v>
+        <v>138</v>
+      </c>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="91">
       <c r="C91" s="1" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="95">
@@ -2178,253 +2720,326 @@
       <c r="E95" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F95" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>8</v>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>131</v>
+        <v>32</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>27</v>
+      <c r="G97" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>135</v>
+        <v>32</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F98" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>27</v>
+      <c r="G98" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>138</v>
+        <v>32</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F99" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>141</v>
+      <c r="G99" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>142</v>
+        <v>152</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>141</v>
+      <c r="G100" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>141</v>
+        <v>24</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>141</v>
+        <v>24</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="C106" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>155</v>
+        <v>24</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
     </row>
     <row r="112">
@@ -2443,313 +3058,422 @@
       <c r="E112" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F112" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>8</v>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>158</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>160</v>
+        <v>169</v>
+      </c>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>161</v>
+        <v>107</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>162</v>
+        <v>12</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>163</v>
+        <v>12</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F115" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>27</v>
+      <c r="G115" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F116" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>141</v>
+      <c r="G116" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F117" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>141</v>
+      <c r="G117" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B119" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="D119" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>138</v>
+        <v>180</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>162</v>
+        <v>12</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>141</v>
+        <v>24</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>162</v>
+        <v>12</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>141</v>
+        <v>50</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>141</v>
+        <v>50</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="F131" s="4">
+        <f>countif(F1:F129, "Top")</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="F132" s="4">
+        <f>countif(F2:F130, "Middle")</f>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A51:G51"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A94:G94"/>
-    <mergeCell ref="A111:G111"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A94:I94"/>
+    <mergeCell ref="A111:I111"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2769,1942 +3493,2382 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>196</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>188</v>
+        <v>29</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0.75</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>188</v>
+        <v>29</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.8125</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>188</v>
+        <v>29</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0.8125</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0.875</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>188</v>
+        <v>29</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0.875</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.9375</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>188</v>
+        <v>29</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0.9375</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0.9895833333333334</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>188</v>
+        <v>48</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.5833333333333334</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>188</v>
+        <v>48</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0.625</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>188</v>
+        <v>48</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.6666666666666666</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>200</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>188</v>
+        <v>48</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0.7083333333333334</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>188</v>
+        <v>48</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.75</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>188</v>
+        <v>48</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0.7916666666666666</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>201</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>188</v>
+        <v>48</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.8333333333333334</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0.5416666666666666</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0.5833333333333334</v>
+        <v>48</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0.8958333333333334</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>196</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="4">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="E15" s="4">
-        <v>0.625</v>
+        <v>48</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0.9895833333333334</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>34</v>
+        <v>203</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0.75</v>
+        <v>63</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0.625</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="E17" s="4">
-        <v>0.8125</v>
+        <v>63</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0.6770833333333334</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0.8125</v>
-      </c>
-      <c r="E18" s="4">
-        <v>0.9895833333333334</v>
+        <v>63</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0.6770833333333334</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0.7291666666666666</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>196</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="4">
-        <v>0.5416666666666666</v>
-      </c>
-      <c r="E19" s="4">
-        <v>0.5833333333333334</v>
+        <v>63</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0.7916666666666666</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="4">
+        <v>29</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="E20" s="5">
         <v>0.5833333333333334</v>
       </c>
-      <c r="E20" s="4">
-        <v>0.625</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>204</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" s="4">
-        <v>0.625</v>
-      </c>
-      <c r="E21" s="4">
+        <v>29</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="E21" s="5">
         <v>0.6666666666666666</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="4">
+        <v>29</v>
+      </c>
+      <c r="D22" s="5">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E22" s="4">
-        <v>0.7291666666666666</v>
+      <c r="E22" s="5">
+        <v>0.75</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" s="4">
-        <v>0.7291666666666666</v>
-      </c>
-      <c r="E23" s="4">
-        <v>0.7916666666666666</v>
+        <v>29</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0.8125</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="4">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="E24" s="4">
-        <v>0.8541666666666666</v>
+        <v>29</v>
+      </c>
+      <c r="D24" s="5">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0.9375</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="4">
-        <v>0.8541666666666666</v>
-      </c>
-      <c r="E25" s="4">
+        <v>29</v>
+      </c>
+      <c r="D25" s="5">
+        <v>0.9375</v>
+      </c>
+      <c r="E25" s="5">
         <v>0.9895833333333334</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>191</v>
+        <v>49</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" s="4">
+        <v>48</v>
+      </c>
+      <c r="D26" s="5">
         <v>0.5416666666666666</v>
       </c>
-      <c r="E26" s="4">
-        <v>0.5625</v>
+      <c r="E26" s="5">
+        <v>0.5833333333333334</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>58</v>
+        <v>205</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D27" s="4">
-        <v>0.5625</v>
-      </c>
-      <c r="E27" s="4">
-        <v>0.59375</v>
+        <v>48</v>
+      </c>
+      <c r="D27" s="5">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="E27" s="5">
+        <v>0.625</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28" s="4">
-        <v>0.59375</v>
-      </c>
-      <c r="E28" s="4">
-        <v>0.75</v>
+        <v>48</v>
+      </c>
+      <c r="D28" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="E28" s="5">
+        <v>0.6666666666666666</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="E29" s="4">
-        <v>0.7916666666666666</v>
+        <v>48</v>
+      </c>
+      <c r="D29" s="5">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E29" s="5">
+        <v>0.7291666666666666</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>188</v>
+        <v>48</v>
+      </c>
+      <c r="D30" s="5">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="E30" s="5">
+        <v>0.7916666666666666</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>66</v>
+        <v>206</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>188</v>
+        <v>48</v>
+      </c>
+      <c r="D31" s="5">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E31" s="5">
+        <v>0.8541666666666666</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>67</v>
+        <v>207</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>188</v>
+        <v>48</v>
+      </c>
+      <c r="D32" s="5">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="E32" s="5">
+        <v>0.9895833333333334</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>208</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>188</v>
+      <c r="D33" s="5">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="E33" s="5">
+        <v>0.5625</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>188</v>
+      <c r="D34" s="5">
+        <v>0.5625</v>
+      </c>
+      <c r="E34" s="5">
+        <v>0.59375</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>188</v>
+      <c r="D35" s="5">
+        <v>0.59375</v>
+      </c>
+      <c r="E35" s="5">
+        <v>0.75</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>72</v>
+        <v>209</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>188</v>
+      <c r="D36" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="E36" s="5">
+        <v>0.7916666666666666</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>63</v>
+        <v>210</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>188</v>
+        <v>29</v>
+      </c>
+      <c r="D37" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="E37" s="5">
+        <v>0.6875</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38" s="4">
-        <v>0.625</v>
-      </c>
-      <c r="E38" s="4">
+        <v>29</v>
+      </c>
+      <c r="D38" s="5">
         <v>0.6875</v>
       </c>
+      <c r="E38" s="5">
+        <v>0.7395833333333334</v>
+      </c>
       <c r="F38" s="1" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39" s="4">
-        <v>0.6875</v>
-      </c>
-      <c r="E39" s="4">
+        <v>29</v>
+      </c>
+      <c r="D39" s="5">
         <v>0.7395833333333334</v>
       </c>
+      <c r="E39" s="5">
+        <v>0.7916666666666666</v>
+      </c>
       <c r="F39" s="1" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" s="4">
-        <v>0.7395833333333334</v>
-      </c>
-      <c r="E40" s="4">
+        <v>29</v>
+      </c>
+      <c r="D40" s="5">
         <v>0.7916666666666666</v>
       </c>
+      <c r="E40" s="5">
+        <v>0.8541666666666666</v>
+      </c>
       <c r="F40" s="1" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D41" s="4">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="E41" s="4">
+        <v>29</v>
+      </c>
+      <c r="D41" s="5">
         <v>0.8541666666666666</v>
       </c>
+      <c r="E41" s="5">
+        <v>0.9166666666666666</v>
+      </c>
       <c r="F41" s="1" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="4">
-        <v>0.8541666666666666</v>
-      </c>
-      <c r="E42" s="4">
+        <v>29</v>
+      </c>
+      <c r="D42" s="5">
         <v>0.9166666666666666</v>
       </c>
+      <c r="E42" s="5">
+        <v>0.9791666666666666</v>
+      </c>
       <c r="F42" s="1" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D43" s="4">
-        <v>0.9166666666666666</v>
-      </c>
-      <c r="E43" s="4">
-        <v>0.9791666666666666</v>
+        <v>48</v>
+      </c>
+      <c r="D43" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="E43" s="5">
+        <v>0.5520833333333334</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D44" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="E44" s="4">
+        <v>48</v>
+      </c>
+      <c r="D44" s="5">
         <v>0.5520833333333334</v>
       </c>
+      <c r="E44" s="5">
+        <v>0.6041666666666666</v>
+      </c>
       <c r="F44" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D45" s="4">
-        <v>0.5520833333333334</v>
-      </c>
-      <c r="E45" s="4">
+        <v>48</v>
+      </c>
+      <c r="D45" s="5">
         <v>0.6041666666666666</v>
       </c>
+      <c r="E45" s="5">
+        <v>0.65625</v>
+      </c>
       <c r="F45" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D46" s="4">
-        <v>0.6041666666666666</v>
-      </c>
-      <c r="E46" s="4">
+        <v>48</v>
+      </c>
+      <c r="D46" s="5">
         <v>0.65625</v>
       </c>
+      <c r="E46" s="5">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="F46" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D47" s="4">
-        <v>0.65625</v>
-      </c>
-      <c r="E47" s="4">
+        <v>48</v>
+      </c>
+      <c r="D47" s="5">
         <v>0.7083333333333334</v>
       </c>
+      <c r="E47" s="5">
+        <v>0.7604166666666666</v>
+      </c>
       <c r="F47" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D48" s="4">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="E48" s="4">
+        <v>48</v>
+      </c>
+      <c r="D48" s="5">
         <v>0.7604166666666666</v>
       </c>
+      <c r="E48" s="5">
+        <v>0.8125</v>
+      </c>
       <c r="F48" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D49" s="4">
-        <v>0.7604166666666666</v>
-      </c>
-      <c r="E49" s="4">
+        <v>48</v>
+      </c>
+      <c r="D49" s="5">
         <v>0.8125</v>
       </c>
+      <c r="E49" s="5">
+        <v>0.84375</v>
+      </c>
       <c r="F49" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D50" s="5">
-        <v>0.8125</v>
-      </c>
-      <c r="E50" s="4">
         <v>0.84375</v>
       </c>
+      <c r="E50" s="5">
+        <v>0.8958333333333334</v>
+      </c>
       <c r="F50" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D51" s="4">
-        <v>0.84375</v>
-      </c>
-      <c r="E51" s="4">
+        <v>48</v>
+      </c>
+      <c r="D51" s="5">
         <v>0.8958333333333334</v>
       </c>
+      <c r="E51" s="5">
+        <v>0.9479166666666666</v>
+      </c>
       <c r="F51" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D52" s="4">
-        <v>0.8958333333333334</v>
-      </c>
-      <c r="E52" s="4">
+        <v>48</v>
+      </c>
+      <c r="D52" s="5">
         <v>0.9479166666666666</v>
       </c>
+      <c r="E52" s="5">
+        <v>0.0</v>
+      </c>
       <c r="F52" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D53" s="4">
-        <v>0.9479166666666666</v>
-      </c>
-      <c r="E53" s="4">
-        <v>0.0</v>
+        <v>63</v>
+      </c>
+      <c r="D53" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="E53" s="5">
+        <v>0.5833333333333334</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D54" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="E54" s="4">
+        <v>63</v>
+      </c>
+      <c r="D54" s="5">
         <v>0.5833333333333334</v>
       </c>
+      <c r="E54" s="5">
+        <v>0.6354166666666666</v>
+      </c>
       <c r="F54" s="1" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D55" s="4">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="E55" s="4">
+        <v>63</v>
+      </c>
+      <c r="D55" s="5">
         <v>0.6354166666666666</v>
       </c>
+      <c r="E55" s="5">
+        <v>0.7083333333333334</v>
+      </c>
       <c r="F55" s="1" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D56" s="4">
-        <v>0.6354166666666666</v>
-      </c>
-      <c r="E56" s="4">
+        <v>63</v>
+      </c>
+      <c r="D56" s="5">
         <v>0.7083333333333334</v>
       </c>
+      <c r="E56" s="5">
+        <v>0.7916666666666666</v>
+      </c>
       <c r="F56" s="1" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>115</v>
+        <v>213</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D57" s="4">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="E57" s="4">
-        <v>0.7916666666666666</v>
+        <v>29</v>
+      </c>
+      <c r="D57" s="5">
+        <v>0.6145833333333334</v>
+      </c>
+      <c r="E57" s="5">
+        <v>0.6666666666666666</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>188</v>
+        <v>29</v>
+      </c>
+      <c r="D58" s="5">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E58" s="5">
+        <v>0.71875</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>188</v>
+        <v>29</v>
+      </c>
+      <c r="D59" s="5">
+        <v>0.71875</v>
+      </c>
+      <c r="E59" s="5">
+        <v>0.7708333333333334</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
-        <v>118</v>
+        <v>215</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>188</v>
+        <v>29</v>
+      </c>
+      <c r="D60" s="5">
+        <v>0.7708333333333334</v>
+      </c>
+      <c r="E60" s="5">
+        <v>0.8229166666666666</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>188</v>
+        <v>29</v>
+      </c>
+      <c r="D61" s="5">
+        <v>0.8229166666666666</v>
+      </c>
+      <c r="E61" s="5">
+        <v>0.875</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>188</v>
+        <v>29</v>
+      </c>
+      <c r="D62" s="5">
+        <v>0.875</v>
+      </c>
+      <c r="E62" s="5">
+        <v>0.9270833333333334</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>120</v>
+        <v>214</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>188</v>
+        <v>29</v>
+      </c>
+      <c r="D63" s="5">
+        <v>0.9270833333333334</v>
+      </c>
+      <c r="E63" s="5">
+        <v>0.9895833333333334</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>121</v>
+        <v>216</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>188</v>
+        <v>48</v>
+      </c>
+      <c r="D64" s="5">
+        <v>0.53125</v>
+      </c>
+      <c r="E64" s="5">
+        <v>0.5833333333333334</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>188</v>
+        <v>48</v>
+      </c>
+      <c r="D65" s="5">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="E65" s="5">
+        <v>0.6354166666666666</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>123</v>
+        <v>217</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>188</v>
+        <v>48</v>
+      </c>
+      <c r="D66" s="5">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="E66" s="5">
+        <v>0.6875</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>124</v>
+        <v>215</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>188</v>
+        <v>48</v>
+      </c>
+      <c r="D67" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="E67" s="5">
+        <v>0.7395833333333334</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>188</v>
+        <v>48</v>
+      </c>
+      <c r="D68" s="5">
+        <v>0.7395833333333334</v>
+      </c>
+      <c r="E68" s="5">
+        <v>0.78125</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>126</v>
+        <v>218</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>188</v>
+        <v>48</v>
+      </c>
+      <c r="D69" s="5">
+        <v>0.78125</v>
+      </c>
+      <c r="E69" s="5">
+        <v>0.8333333333333334</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>188</v>
+        <v>48</v>
+      </c>
+      <c r="D70" s="5">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E70" s="5">
+        <v>0.9166666666666666</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>131</v>
+        <v>219</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D71" s="4">
-        <v>0.6458333333333334</v>
-      </c>
-      <c r="E71" s="4">
-        <v>0.6979166666666666</v>
+        <v>48</v>
+      </c>
+      <c r="D71" s="5">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="E71" s="5">
+        <v>0.0</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D72" s="4">
-        <v>0.71875</v>
-      </c>
-      <c r="E72" s="4">
-        <v>0.7708333333333334</v>
+        <v>63</v>
+      </c>
+      <c r="D72" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="E72" s="5">
+        <v>0.7916666666666666</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D73" s="4">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="E73" s="4">
-        <v>0.84375</v>
+        <v>29</v>
+      </c>
+      <c r="D73" s="5">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="E73" s="5">
+        <v>0.6979166666666666</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D74" s="4">
-        <v>0.8645833333333334</v>
-      </c>
-      <c r="E74" s="4">
-        <v>0.9166666666666666</v>
+        <v>29</v>
+      </c>
+      <c r="D74" s="5">
+        <v>0.71875</v>
+      </c>
+      <c r="E74" s="5">
+        <v>0.7708333333333334</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D75" s="4">
-        <v>0.9270833333333334</v>
-      </c>
-      <c r="E75" s="4">
-        <v>0.9895833333333334</v>
+        <v>29</v>
+      </c>
+      <c r="D75" s="5">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E75" s="5">
+        <v>0.84375</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D76" s="4">
-        <v>0.5625</v>
-      </c>
-      <c r="E76" s="4">
-        <v>0.6145833333333334</v>
+        <v>29</v>
+      </c>
+      <c r="D76" s="5">
+        <v>0.8645833333333334</v>
+      </c>
+      <c r="E76" s="5">
+        <v>0.9166666666666666</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D77" s="4">
-        <v>0.6354166666666666</v>
-      </c>
-      <c r="E77" s="4">
-        <v>0.6875</v>
+        <v>29</v>
+      </c>
+      <c r="D77" s="5">
+        <v>0.9270833333333334</v>
+      </c>
+      <c r="E77" s="5">
+        <v>0.9895833333333334</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D78" s="4">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="E78" s="4">
-        <v>0.7604166666666666</v>
+        <v>48</v>
+      </c>
+      <c r="D78" s="5">
+        <v>0.5625</v>
+      </c>
+      <c r="E78" s="5">
+        <v>0.6145833333333334</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D79" s="4">
-        <v>0.78125</v>
-      </c>
-      <c r="E79" s="4">
-        <v>0.8229166666666666</v>
+        <v>48</v>
+      </c>
+      <c r="D79" s="5">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="E79" s="5">
+        <v>0.6875</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D80" s="4">
-        <v>0.84375</v>
-      </c>
-      <c r="E80" s="4">
-        <v>0.8958333333333334</v>
+        <v>48</v>
+      </c>
+      <c r="D80" s="5">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="E80" s="5">
+        <v>0.7604166666666666</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>189</v>
+        <v>223</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D81" s="4">
-        <v>0.8958333333333334</v>
-      </c>
-      <c r="E81" s="4">
-        <v>0.9791666666666666</v>
+        <v>48</v>
+      </c>
+      <c r="D81" s="5">
+        <v>0.78125</v>
+      </c>
+      <c r="E81" s="5">
+        <v>0.8229166666666666</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>189</v>
+        <v>223</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>69</v>
+        <v>163</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D82" s="4">
-        <v>0.9791666666666666</v>
-      </c>
-      <c r="E82" s="4">
-        <v>0.020833333333333332</v>
+        <v>48</v>
+      </c>
+      <c r="D82" s="5">
+        <v>0.84375</v>
+      </c>
+      <c r="E82" s="5">
+        <v>0.8958333333333334</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D83" s="4">
-        <v>0.6354166666666666</v>
-      </c>
-      <c r="E83" s="4">
-        <v>0.65625</v>
+        <v>48</v>
+      </c>
+      <c r="D83" s="5">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="E83" s="5">
+        <v>0.9791666666666666</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D84" s="4">
-        <v>0.6770833333333334</v>
-      </c>
-      <c r="E84" s="4">
-        <v>0.7395833333333334</v>
+        <v>48</v>
+      </c>
+      <c r="D84" s="5">
+        <v>0.9791666666666666</v>
+      </c>
+      <c r="E84" s="5">
+        <v>0.0</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="s">
-        <v>165</v>
+        <v>213</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D85" s="4">
-        <v>0.7604166666666666</v>
-      </c>
-      <c r="E85" s="4">
-        <v>0.8229166666666666</v>
+        <v>29</v>
+      </c>
+      <c r="D85" s="5">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="E85" s="5">
+        <v>0.65625</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D86" s="4">
-        <v>0.84375</v>
-      </c>
-      <c r="E86" s="4">
-        <v>0.90625</v>
+        <v>29</v>
+      </c>
+      <c r="D86" s="5">
+        <v>0.6770833333333334</v>
+      </c>
+      <c r="E86" s="5">
+        <v>0.7395833333333334</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D87" s="4">
-        <v>0.9270833333333334</v>
-      </c>
-      <c r="E87" s="4">
-        <v>0.9895833333333334</v>
+        <v>29</v>
+      </c>
+      <c r="D87" s="5">
+        <v>0.7604166666666666</v>
+      </c>
+      <c r="E87" s="5">
+        <v>0.8229166666666666</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D88" s="4">
-        <v>0.5520833333333334</v>
-      </c>
-      <c r="E88" s="4">
-        <v>0.59375</v>
+        <v>29</v>
+      </c>
+      <c r="D88" s="5">
+        <v>0.84375</v>
+      </c>
+      <c r="E88" s="5">
+        <v>0.90625</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="s">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D89" s="4">
-        <v>0.6145833333333334</v>
-      </c>
-      <c r="E89" s="4">
-        <v>0.6770833333333334</v>
+        <v>29</v>
+      </c>
+      <c r="D89" s="5">
+        <v>0.9270833333333334</v>
+      </c>
+      <c r="E89" s="5">
+        <v>0.9895833333333334</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D90" s="4">
-        <v>0.6979166666666666</v>
-      </c>
-      <c r="E90" s="4">
-        <v>0.7604166666666666</v>
+        <v>48</v>
+      </c>
+      <c r="D90" s="5">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="E90" s="5">
+        <v>0.59375</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D91" s="4">
-        <v>0.78125</v>
-      </c>
-      <c r="E91" s="4">
-        <v>0.84375</v>
+        <v>48</v>
+      </c>
+      <c r="D91" s="5">
+        <v>0.6145833333333334</v>
+      </c>
+      <c r="E91" s="5">
+        <v>0.6770833333333334</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D92" s="4">
-        <v>0.8645833333333334</v>
-      </c>
-      <c r="E92" s="4">
-        <v>0.9270833333333334</v>
+        <v>48</v>
+      </c>
+      <c r="D92" s="5">
+        <v>0.6979166666666666</v>
+      </c>
+      <c r="E92" s="5">
+        <v>0.7604166666666666</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D93" s="4">
-        <v>0.9479166666666666</v>
-      </c>
-      <c r="E93" s="4">
-        <v>0.0</v>
+        <v>48</v>
+      </c>
+      <c r="D93" s="5">
+        <v>0.78125</v>
+      </c>
+      <c r="E93" s="5">
+        <v>0.84375</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D94" s="4">
-        <v>0.5625</v>
-      </c>
-      <c r="E94" s="4">
-        <v>0.6145833333333334</v>
+        <v>48</v>
+      </c>
+      <c r="D94" s="5">
+        <v>0.8645833333333334</v>
+      </c>
+      <c r="E94" s="5">
+        <v>0.9270833333333334</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="s">
-        <v>142</v>
+        <v>187</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D95" s="4">
-        <v>0.6354166666666666</v>
-      </c>
-      <c r="E95" s="4">
-        <v>0.6875</v>
+        <v>48</v>
+      </c>
+      <c r="D95" s="5">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="E95" s="5">
+        <v>0.0</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D96" s="4">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="E96" s="4">
-        <v>0.7604166666666666</v>
+        <v>63</v>
+      </c>
+      <c r="D96" s="5">
+        <v>0.5625</v>
+      </c>
+      <c r="E96" s="5">
+        <v>0.6145833333333334</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D97" s="4">
+        <v>63</v>
+      </c>
+      <c r="D97" s="5">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="E97" s="5">
+        <v>0.6875</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D98" s="5">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="E98" s="5">
+        <v>0.7604166666666666</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D99" s="5">
         <v>0.78125</v>
       </c>
-      <c r="E97" s="4">
+      <c r="E99" s="5">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D100" s="5">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="E100" s="5">
         <v>0.9166666666666666</v>
       </c>
-      <c r="F97" s="1" t="s">
-        <v>190</v>
+      <c r="F100" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D101" s="5">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="E101" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D102" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="E102" s="5">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D103" s="5">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E103" s="5">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D104" s="5">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="E104" s="5">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D105" s="5">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="E105" s="5">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D106" s="5">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="E106" s="5">
+        <v>0.90625</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D107" s="5">
+        <v>0.90625</v>
+      </c>
+      <c r="E107" s="5">
+        <v>0.9895833333333334</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D108" s="5">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="E108" s="5">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D109" s="5">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E109" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D110" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="E110" s="5">
+        <v>0.8125</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D111" s="5">
+        <v>0.8125</v>
+      </c>
+      <c r="E111" s="5">
+        <v>0.8645833333333334</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D112" s="5">
+        <v>0.8645833333333334</v>
+      </c>
+      <c r="E112" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D113" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="E113" s="5">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D114" s="5">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="E114" s="5">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D115" s="5">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E115" s="5">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D116" s="5">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="E116" s="5">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D117" s="5">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="E117" s="5">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D118" s="5">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="E118" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D119" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="E119" s="5">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/The FullMoon Festival Linup.xlsx
+++ b/The FullMoon Festival Linup.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="238">
   <si>
     <t>THE FULLMOON FESTIVAL</t>
   </si>
@@ -630,6 +630,9 @@
   </si>
   <si>
     <t>T4</t>
+  </si>
+  <si>
+    <t>Skeptiq</t>
   </si>
   <si>
     <t>Alan Stacey / Ste Butt</t>
@@ -3953,7 +3956,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>44</v>
+        <v>205</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>28</v>
@@ -3962,10 +3965,10 @@
         <v>29</v>
       </c>
       <c r="D24" s="5">
-        <v>0.8958333333333334</v>
+        <v>0.8125</v>
       </c>
       <c r="E24" s="5">
-        <v>0.9375</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>198</v>
@@ -3973,7 +3976,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>47</v>
+        <v>206</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>28</v>
@@ -3982,10 +3985,10 @@
         <v>29</v>
       </c>
       <c r="D25" s="5">
-        <v>0.9375</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="E25" s="5">
-        <v>0.9895833333333334</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>198</v>
@@ -3993,19 +3996,19 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D26" s="5">
-        <v>0.5416666666666666</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="E26" s="5">
-        <v>0.5833333333333334</v>
+        <v>0.9375</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>198</v>
@@ -4013,19 +4016,19 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>205</v>
+        <v>47</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D27" s="5">
-        <v>0.5833333333333334</v>
+        <v>0.9375</v>
       </c>
       <c r="E27" s="5">
-        <v>0.625</v>
+        <v>0.9895833333333334</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>198</v>
@@ -4033,7 +4036,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>28</v>
@@ -4042,10 +4045,10 @@
         <v>48</v>
       </c>
       <c r="D28" s="5">
-        <v>0.625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="E28" s="5">
-        <v>0.6666666666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>198</v>
@@ -4053,7 +4056,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>52</v>
+        <v>205</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>28</v>
@@ -4062,10 +4065,10 @@
         <v>48</v>
       </c>
       <c r="D29" s="5">
-        <v>0.6666666666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E29" s="5">
-        <v>0.7291666666666666</v>
+        <v>0.625</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>198</v>
@@ -4073,7 +4076,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>28</v>
@@ -4082,10 +4085,10 @@
         <v>48</v>
       </c>
       <c r="D30" s="5">
-        <v>0.7291666666666666</v>
+        <v>0.625</v>
       </c>
       <c r="E30" s="5">
-        <v>0.7916666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>198</v>
@@ -4093,7 +4096,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>206</v>
+        <v>52</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>28</v>
@@ -4102,10 +4105,10 @@
         <v>48</v>
       </c>
       <c r="D31" s="5">
-        <v>0.7916666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E31" s="5">
-        <v>0.8541666666666666</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>198</v>
@@ -4113,7 +4116,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>207</v>
+        <v>55</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>28</v>
@@ -4122,10 +4125,10 @@
         <v>48</v>
       </c>
       <c r="D32" s="5">
-        <v>0.8541666666666666</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E32" s="5">
-        <v>0.9895833333333334</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>198</v>
@@ -4133,19 +4136,19 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D33" s="5">
-        <v>0.5416666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E33" s="5">
-        <v>0.5625</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>198</v>
@@ -4153,19 +4156,19 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>67</v>
+        <v>208</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D34" s="5">
-        <v>0.5625</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="E34" s="5">
-        <v>0.59375</v>
+        <v>0.9895833333333334</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>198</v>
@@ -4173,7 +4176,7 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>69</v>
+        <v>209</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>28</v>
@@ -4182,10 +4185,10 @@
         <v>63</v>
       </c>
       <c r="D35" s="5">
-        <v>0.59375</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="E35" s="5">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>198</v>
@@ -4193,7 +4196,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>209</v>
+        <v>67</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>28</v>
@@ -4202,10 +4205,10 @@
         <v>63</v>
       </c>
       <c r="D36" s="5">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="E36" s="5">
-        <v>0.7916666666666666</v>
+        <v>0.59375</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>198</v>
@@ -4213,199 +4216,199 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>210</v>
+        <v>28</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="D37" s="5">
-        <v>0.625</v>
+        <v>0.59375</v>
       </c>
       <c r="E37" s="5">
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>88</v>
+        <v>210</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>210</v>
+        <v>28</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="D38" s="5">
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="E38" s="5">
-        <v>0.7395833333333334</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D39" s="5">
-        <v>0.7395833333333334</v>
+        <v>0.625</v>
       </c>
       <c r="E39" s="5">
-        <v>0.7916666666666666</v>
+        <v>0.6875</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D40" s="5">
-        <v>0.7916666666666666</v>
+        <v>0.6875</v>
       </c>
       <c r="E40" s="5">
-        <v>0.8541666666666666</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D41" s="5">
-        <v>0.8541666666666666</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="E41" s="5">
-        <v>0.9166666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D42" s="5">
-        <v>0.9166666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E42" s="5">
-        <v>0.9791666666666666</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D43" s="5">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="E43" s="5">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D43" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="E43" s="5">
-        <v>0.5520833333333334</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" s="5">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="E44" s="5">
+        <v>0.9791666666666666</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D44" s="5">
-        <v>0.5520833333333334</v>
-      </c>
-      <c r="E44" s="5">
-        <v>0.6041666666666666</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D45" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="E45" s="5">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D45" s="5">
-        <v>0.6041666666666666</v>
-      </c>
-      <c r="E45" s="5">
-        <v>0.65625</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D46" s="5">
-        <v>0.65625</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="E46" s="5">
-        <v>0.7083333333333334</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>198</v>
@@ -4413,19 +4416,19 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D47" s="5">
-        <v>0.7083333333333334</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="E47" s="5">
-        <v>0.7604166666666666</v>
+        <v>0.65625</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>198</v>
@@ -4433,19 +4436,19 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D48" s="5">
-        <v>0.7604166666666666</v>
+        <v>0.65625</v>
       </c>
       <c r="E48" s="5">
-        <v>0.8125</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>198</v>
@@ -4453,19 +4456,19 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D49" s="5">
-        <v>0.8125</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E49" s="5">
-        <v>0.84375</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>198</v>
@@ -4473,19 +4476,19 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D50" s="5">
-        <v>0.84375</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="E50" s="5">
-        <v>0.8958333333333334</v>
+        <v>0.8125</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>198</v>
@@ -4493,19 +4496,19 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D51" s="5">
-        <v>0.8958333333333334</v>
+        <v>0.8125</v>
       </c>
       <c r="E51" s="5">
-        <v>0.9479166666666666</v>
+        <v>0.84375</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>198</v>
@@ -4513,19 +4516,19 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D52" s="5">
-        <v>0.9479166666666666</v>
+        <v>0.84375</v>
       </c>
       <c r="E52" s="5">
-        <v>0.0</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>198</v>
@@ -4533,139 +4536,139 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D53" s="5">
-        <v>0.5</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="E53" s="5">
-        <v>0.5833333333333334</v>
+        <v>0.9479166666666666</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D54" s="5">
-        <v>0.5833333333333334</v>
+        <v>0.9479166666666666</v>
       </c>
       <c r="E54" s="5">
-        <v>0.6354166666666666</v>
+        <v>0.0</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D55" s="5">
-        <v>0.6354166666666666</v>
+        <v>0.5</v>
       </c>
       <c r="E55" s="5">
-        <v>0.7083333333333334</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D56" s="5">
-        <v>0.7083333333333334</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E56" s="5">
-        <v>0.7916666666666666</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>213</v>
+        <v>124</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="D57" s="5">
-        <v>0.6145833333333334</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="E57" s="5">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="D58" s="5">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E58" s="5">
-        <v>0.71875</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>79</v>
+        <v>214</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D59" s="5">
-        <v>0.71875</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="E59" s="5">
-        <v>0.7708333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>198</v>
@@ -4673,19 +4676,19 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="C60" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D60" s="5">
-        <v>0.7708333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E60" s="5">
-        <v>0.8229166666666666</v>
+        <v>0.71875</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>198</v>
@@ -4693,19 +4696,19 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D61" s="5">
-        <v>0.8229166666666666</v>
+        <v>0.71875</v>
       </c>
       <c r="E61" s="5">
-        <v>0.875</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>198</v>
@@ -4713,19 +4716,19 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D62" s="5">
-        <v>0.875</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="E62" s="5">
-        <v>0.9270833333333334</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>198</v>
@@ -4733,19 +4736,19 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>214</v>
+        <v>114</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D63" s="5">
-        <v>0.9270833333333334</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="E63" s="5">
-        <v>0.9895833333333334</v>
+        <v>0.875</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>198</v>
@@ -4753,19 +4756,19 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="s">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D64" s="5">
-        <v>0.53125</v>
+        <v>0.875</v>
       </c>
       <c r="E64" s="5">
-        <v>0.5833333333333334</v>
+        <v>0.9270833333333334</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>198</v>
@@ -4773,19 +4776,19 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>133</v>
+        <v>215</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D65" s="5">
-        <v>0.5833333333333334</v>
+        <v>0.9270833333333334</v>
       </c>
       <c r="E65" s="5">
-        <v>0.6354166666666666</v>
+        <v>0.9895833333333334</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>198</v>
@@ -4796,16 +4799,16 @@
         <v>217</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D66" s="5">
-        <v>0.6354166666666666</v>
+        <v>0.53125</v>
       </c>
       <c r="E66" s="5">
-        <v>0.6875</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>198</v>
@@ -4813,19 +4816,19 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="C67" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D67" s="5">
-        <v>0.6875</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E67" s="5">
-        <v>0.7395833333333334</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>198</v>
@@ -4833,19 +4836,19 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="s">
-        <v>129</v>
+        <v>218</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D68" s="5">
-        <v>0.7395833333333334</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="E68" s="5">
-        <v>0.78125</v>
+        <v>0.6875</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>198</v>
@@ -4853,19 +4856,19 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D69" s="5">
-        <v>0.78125</v>
+        <v>0.6875</v>
       </c>
       <c r="E69" s="5">
-        <v>0.8333333333333334</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>198</v>
@@ -4873,19 +4876,19 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D70" s="5">
-        <v>0.8333333333333334</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="E70" s="5">
-        <v>0.9166666666666666</v>
+        <v>0.78125</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>198</v>
@@ -4896,16 +4899,16 @@
         <v>219</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D71" s="5">
-        <v>0.9166666666666666</v>
+        <v>0.78125</v>
       </c>
       <c r="E71" s="5">
-        <v>0.0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>198</v>
@@ -4913,19 +4916,19 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>220</v>
+        <v>139</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D72" s="5">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E72" s="5">
-        <v>0.7916666666666666</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>198</v>
@@ -4933,239 +4936,239 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>142</v>
+        <v>220</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D73" s="5">
-        <v>0.6458333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="E73" s="5">
-        <v>0.6979166666666666</v>
+        <v>0.0</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>145</v>
+        <v>221</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>222</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="D74" s="5">
-        <v>0.71875</v>
+        <v>0.5</v>
       </c>
       <c r="E74" s="5">
-        <v>0.7708333333333334</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D75" s="5">
-        <v>0.7916666666666666</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="E75" s="5">
-        <v>0.84375</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D76" s="5">
-        <v>0.8645833333333334</v>
+        <v>0.71875</v>
       </c>
       <c r="E76" s="5">
-        <v>0.9166666666666666</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D77" s="5">
-        <v>0.9270833333333334</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E77" s="5">
-        <v>0.9895833333333334</v>
+        <v>0.84375</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D78" s="5">
-        <v>0.5625</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="E78" s="5">
-        <v>0.6145833333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D79" s="5">
-        <v>0.6354166666666666</v>
+        <v>0.9270833333333334</v>
       </c>
       <c r="E79" s="5">
-        <v>0.6875</v>
+        <v>0.9895833333333334</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D80" s="5">
-        <v>0.7083333333333334</v>
+        <v>0.5625</v>
       </c>
       <c r="E80" s="5">
-        <v>0.7604166666666666</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D81" s="5">
-        <v>0.78125</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="E81" s="5">
-        <v>0.8229166666666666</v>
+        <v>0.6875</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D82" s="5">
-        <v>0.84375</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E82" s="5">
-        <v>0.8958333333333334</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D83" s="5">
-        <v>0.8958333333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="E83" s="5">
-        <v>0.9791666666666666</v>
+        <v>0.8229166666666666</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="s">
-        <v>79</v>
+        <v>163</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D84" s="5">
-        <v>0.9791666666666666</v>
+        <v>0.84375</v>
       </c>
       <c r="E84" s="5">
-        <v>0.0</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>198</v>
@@ -5173,359 +5176,359 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="s">
-        <v>213</v>
+        <v>165</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D85" s="5">
-        <v>0.6354166666666666</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="E85" s="5">
-        <v>0.65625</v>
+        <v>0.9791666666666666</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="s">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D86" s="5">
-        <v>0.6770833333333334</v>
+        <v>0.9791666666666666</v>
       </c>
       <c r="E86" s="5">
-        <v>0.7395833333333334</v>
+        <v>0.0</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
-        <v>174</v>
+        <v>214</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D87" s="5">
+        <v>0.6354166666666666</v>
+      </c>
+      <c r="E87" s="5">
+        <v>0.65625</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D87" s="5">
-        <v>0.7604166666666666</v>
-      </c>
-      <c r="E87" s="5">
-        <v>0.8229166666666666</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="B88" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D88" s="5">
+        <v>0.6770833333333334</v>
+      </c>
+      <c r="E88" s="5">
+        <v>0.7395833333333334</v>
+      </c>
+      <c r="F88" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D88" s="5">
-        <v>0.84375</v>
-      </c>
-      <c r="E88" s="5">
-        <v>0.90625</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D89" s="5">
+        <v>0.7604166666666666</v>
+      </c>
+      <c r="E89" s="5">
+        <v>0.8229166666666666</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D89" s="5">
-        <v>0.9270833333333334</v>
-      </c>
-      <c r="E89" s="5">
-        <v>0.9895833333333334</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B90" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D90" s="5">
+        <v>0.84375</v>
+      </c>
+      <c r="E90" s="5">
+        <v>0.90625</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D90" s="5">
-        <v>0.5520833333333334</v>
-      </c>
-      <c r="E90" s="5">
-        <v>0.59375</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D91" s="5">
+        <v>0.9270833333333334</v>
+      </c>
+      <c r="E91" s="5">
+        <v>0.9895833333333334</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D91" s="5">
-        <v>0.6145833333333334</v>
-      </c>
-      <c r="E91" s="5">
-        <v>0.6770833333333334</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="B92" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D92" s="5">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="E92" s="5">
+        <v>0.59375</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D92" s="5">
-        <v>0.6979166666666666</v>
-      </c>
-      <c r="E92" s="5">
-        <v>0.7604166666666666</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="B93" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D93" s="5">
+        <v>0.6145833333333334</v>
+      </c>
+      <c r="E93" s="5">
+        <v>0.6770833333333334</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D93" s="5">
-        <v>0.78125</v>
-      </c>
-      <c r="E93" s="5">
-        <v>0.84375</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B94" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D94" s="5">
+        <v>0.6979166666666666</v>
+      </c>
+      <c r="E94" s="5">
+        <v>0.7604166666666666</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D94" s="5">
-        <v>0.8645833333333334</v>
-      </c>
-      <c r="E94" s="5">
-        <v>0.9270833333333334</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B95" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D95" s="5">
+        <v>0.78125</v>
+      </c>
+      <c r="E95" s="5">
+        <v>0.84375</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D95" s="5">
-        <v>0.9479166666666666</v>
-      </c>
-      <c r="E95" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B96" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D96" s="5">
+        <v>0.8645833333333334</v>
+      </c>
+      <c r="E96" s="5">
+        <v>0.9270833333333334</v>
+      </c>
+      <c r="F96" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D96" s="5">
-        <v>0.5625</v>
-      </c>
-      <c r="E96" s="5">
-        <v>0.6145833333333334</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="B97" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D97" s="5">
+        <v>0.9479166666666666</v>
+      </c>
+      <c r="E97" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D97" s="5">
-        <v>0.6354166666666666</v>
-      </c>
-      <c r="E97" s="5">
-        <v>0.6875</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="s">
-        <v>148</v>
+        <v>188</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D98" s="5">
-        <v>0.7083333333333334</v>
+        <v>0.5625</v>
       </c>
       <c r="E98" s="5">
-        <v>0.7604166666666666</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D99" s="5">
-        <v>0.78125</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="E99" s="5">
-        <v>0.8333333333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D100" s="5">
-        <v>0.8333333333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E100" s="5">
-        <v>0.9166666666666666</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
-        <v>226</v>
+        <v>160</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="D101" s="5">
-        <v>0.5833333333333334</v>
+        <v>0.78125</v>
       </c>
       <c r="E101" s="5">
-        <v>0.625</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
-        <v>80</v>
+        <v>226</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="D102" s="5">
-        <v>0.625</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E102" s="5">
-        <v>0.6666666666666666</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>198</v>
@@ -5533,19 +5536,19 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D103" s="5">
-        <v>0.6666666666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E103" s="5">
-        <v>0.7291666666666666</v>
+        <v>0.625</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>198</v>
@@ -5553,19 +5556,19 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D104" s="5">
-        <v>0.7291666666666666</v>
+        <v>0.625</v>
       </c>
       <c r="E104" s="5">
-        <v>0.7916666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>198</v>
@@ -5573,19 +5576,19 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>76</v>
+        <v>229</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D105" s="5">
-        <v>0.7916666666666666</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E105" s="5">
-        <v>0.8541666666666666</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>198</v>
@@ -5593,19 +5596,19 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D106" s="5">
-        <v>0.8541666666666666</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="E106" s="5">
-        <v>0.90625</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>198</v>
@@ -5613,19 +5616,19 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D107" s="5">
-        <v>0.90625</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="E107" s="5">
-        <v>0.9895833333333334</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>198</v>
@@ -5636,16 +5639,16 @@
         <v>73</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D108" s="5">
-        <v>0.5833333333333334</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="E108" s="5">
-        <v>0.6666666666666666</v>
+        <v>0.90625</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>198</v>
@@ -5653,19 +5656,19 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D109" s="5">
-        <v>0.6666666666666666</v>
+        <v>0.90625</v>
       </c>
       <c r="E109" s="5">
-        <v>0.75</v>
+        <v>0.9895833333333334</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>198</v>
@@ -5673,19 +5676,19 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D110" s="5">
-        <v>0.75</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E110" s="5">
-        <v>0.8125</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>198</v>
@@ -5693,19 +5696,19 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D111" s="5">
-        <v>0.8125</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E111" s="5">
-        <v>0.8645833333333334</v>
+        <v>0.75</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>198</v>
@@ -5713,19 +5716,19 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="s">
-        <v>229</v>
+        <v>81</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D112" s="5">
-        <v>0.8645833333333334</v>
+        <v>0.75</v>
       </c>
       <c r="E112" s="5">
-        <v>0.0</v>
+        <v>0.8125</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>198</v>
@@ -5736,16 +5739,16 @@
         <v>78</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D113" s="5">
-        <v>0.5</v>
+        <v>0.8125</v>
       </c>
       <c r="E113" s="5">
-        <v>0.5833333333333334</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>198</v>
@@ -5753,19 +5756,19 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
-        <v>82</v>
+        <v>230</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D114" s="5">
-        <v>0.5833333333333334</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="E114" s="5">
-        <v>0.6666666666666666</v>
+        <v>0.0</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>198</v>
@@ -5773,19 +5776,19 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
-        <v>230</v>
+        <v>78</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D115" s="5">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="E115" s="5">
-        <v>0.7916666666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>198</v>
@@ -5793,82 +5796,122 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="s">
-        <v>231</v>
+        <v>82</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D116" s="5">
-        <v>0.4166666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="E116" s="5">
-        <v>0.4548611111111111</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>233</v>
+        <v>198</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D117" s="5">
-        <v>0.4583333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E117" s="5">
-        <v>0.4791666666666667</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>233</v>
+        <v>198</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D118" s="5">
-        <v>0.4791666666666667</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="E118" s="5">
-        <v>0.5</v>
+        <v>0.4548611111111111</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D119" s="5">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="E119" s="5">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D120" s="5">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="E120" s="5">
         <v>0.5</v>
       </c>
-      <c r="E119" s="5">
+      <c r="F120" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D121" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="E121" s="5">
         <v>0.5833333333333334</v>
       </c>
-      <c r="F119" s="1" t="s">
-        <v>233</v>
+      <c r="F121" s="1" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/The FullMoon Festival Linup.xlsx
+++ b/The FullMoon Festival Linup.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="238">
   <si>
     <t>THE FULLMOON FESTIVAL</t>
   </si>
@@ -5842,7 +5842,7 @@
         <v>233</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D118" s="5">
         <v>0.4166666666666667</v>
@@ -5862,7 +5862,7 @@
         <v>233</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D119" s="5">
         <v>0.4583333333333333</v>
@@ -5882,7 +5882,7 @@
         <v>233</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D120" s="5">
         <v>0.4791666666666667</v>
@@ -5902,7 +5902,7 @@
         <v>233</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D121" s="5">
         <v>0.5</v>
@@ -5911,6 +5911,86 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="F121" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D122" s="5">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="E122" s="5">
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D123" s="5">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="E123" s="5">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D124" s="5">
+        <v>0.4791666666666667</v>
+      </c>
+      <c r="E124" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D125" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="E125" s="5">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="F125" s="1" t="s">
         <v>234</v>
       </c>
     </row>

--- a/The FullMoon Festival Linup.xlsx
+++ b/The FullMoon Festival Linup.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="239">
   <si>
     <t>THE FULLMOON FESTIVAL</t>
   </si>
@@ -687,6 +687,9 @@
   </si>
   <si>
     <t>Band</t>
+  </si>
+  <si>
+    <t>Under The Bed</t>
   </si>
   <si>
     <t>The Pub</t>
@@ -5216,10 +5219,10 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>29</v>
@@ -5228,7 +5231,7 @@
         <v>0.6354166666666666</v>
       </c>
       <c r="E87" s="5">
-        <v>0.65625</v>
+        <v>0.6875</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>224</v>
@@ -5239,16 +5242,16 @@
         <v>146</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D88" s="5">
-        <v>0.6770833333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E88" s="5">
-        <v>0.7395833333333334</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>224</v>
@@ -5259,16 +5262,16 @@
         <v>174</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D89" s="5">
-        <v>0.7604166666666666</v>
+        <v>0.78125</v>
       </c>
       <c r="E89" s="5">
-        <v>0.8229166666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>224</v>
@@ -5279,13 +5282,13 @@
         <v>176</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D90" s="5">
-        <v>0.84375</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="E90" s="5">
         <v>0.90625</v>
@@ -5299,7 +5302,7 @@
         <v>177</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>29</v>
@@ -5319,7 +5322,7 @@
         <v>169</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>48</v>
@@ -5339,7 +5342,7 @@
         <v>149</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>48</v>
@@ -5359,7 +5362,7 @@
         <v>182</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>48</v>
@@ -5379,7 +5382,7 @@
         <v>184</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>48</v>
@@ -5399,7 +5402,7 @@
         <v>186</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>48</v>
@@ -5419,7 +5422,7 @@
         <v>187</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>48</v>
@@ -5439,7 +5442,7 @@
         <v>188</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>63</v>
@@ -5459,7 +5462,7 @@
         <v>153</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>63</v>
@@ -5479,7 +5482,7 @@
         <v>148</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>63</v>
@@ -5499,7 +5502,7 @@
         <v>160</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>63</v>
@@ -5516,10 +5519,10 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>225</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>63</v>
@@ -5536,10 +5539,10 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>29</v>
@@ -5559,7 +5562,7 @@
         <v>80</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>29</v>
@@ -5576,10 +5579,10 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>228</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>29</v>
@@ -5599,7 +5602,7 @@
         <v>81</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>29</v>
@@ -5619,7 +5622,7 @@
         <v>76</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>29</v>
@@ -5639,7 +5642,7 @@
         <v>73</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>29</v>
@@ -5659,7 +5662,7 @@
         <v>77</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>29</v>
@@ -5679,7 +5682,7 @@
         <v>73</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>48</v>
@@ -5699,7 +5702,7 @@
         <v>82</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>48</v>
@@ -5719,7 +5722,7 @@
         <v>81</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>48</v>
@@ -5739,7 +5742,7 @@
         <v>78</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>48</v>
@@ -5756,10 +5759,10 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>48</v>
@@ -5779,7 +5782,7 @@
         <v>78</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>63</v>
@@ -5799,7 +5802,7 @@
         <v>82</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>63</v>
@@ -5816,10 +5819,10 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>63</v>
@@ -5836,10 +5839,10 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>48</v>
@@ -5851,15 +5854,15 @@
         <v>0.4548611111111111</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>48</v>
@@ -5871,15 +5874,15 @@
         <v>0.4791666666666667</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>48</v>
@@ -5891,15 +5894,15 @@
         <v>0.5</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>48</v>
@@ -5911,15 +5914,15 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>63</v>
@@ -5931,15 +5934,15 @@
         <v>0.4548611111111111</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>63</v>
@@ -5951,15 +5954,15 @@
         <v>0.4791666666666667</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>63</v>
@@ -5971,15 +5974,15 @@
         <v>0.5</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>63</v>
@@ -5991,7 +5994,7 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
